--- a/05-automation-vba/05-events-userforms-automation/5.5-events-userforms-automation.xlsx
+++ b/05-automation-vba/05-events-userforms-automation/5.5-events-userforms-automation.xlsx
@@ -851,7 +851,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -859,7 +859,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 36 rows — Excel Table 'tblBeds'</t>
+          <t>Data: 36 rows, in the Excel Table 'tblBeds'</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 69 rows — Excel Table 'tblIntake'</t>
+          <t>Data: 69 rows, in the Excel Table 'tblIntake'</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1083,7 +1083,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against, and column D shows a sample solution (steps or code).</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>`Application.EnableEvents = True` (type it in the Immediate window and press Enter)</t>
+          <t>Application.EnableEvents = True (type it in the Immediate window and press Enter)</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D7" s="39" t="inlineStr">
         <is>
-          <t>`CensusReport_2025-12-31_1707.xlsm`</t>
+          <t>CensusReport_2025-12-31_1707.xlsm</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>**A.** SaveCopyAs writes a snapshot to a new file and leaves the open workbook alone.</t>
+          <t>A. SaveCopyAs writes a snapshot to a new file and leaves the open workbook alone.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>**C.** A scheduled (Recurrence) Power Automate flow runs an Office Script in the cloud.</t>
+          <t>C. A scheduled (Recurrence) Power Automate flow runs an Office Script in the cloud.</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1678,7 +1678,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against, and column D shows a sample solution (steps or code).</t>
         </is>
       </c>
     </row>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="199" customHeight="1">
+    <row r="2" ht="184" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>The Chief Nursing Officer wants a monthly census packet without anyone copying and pasting. Write BuildCensusReport in modReports. It reads the month from Settings!B3 (ReportMonth) and then:

--- a/05-automation-vba/05-events-userforms-automation/5.5-events-userforms-automation.xlsx
+++ b/05-automation-vba/05-events-userforms-automation/5.5-events-userforms-automation.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -757,7 +757,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Expert  ·  about 75 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Expert  ·  about 195 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1004,46 +1004,70 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>BedBoard</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 36 rows, in the Excel Table 'tblBeds'</t>
+          <t>12 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
+          <t>BedBoard</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Data: 36 rows, in the Excel Table 'tblBeds'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Data: 69 rows, in the Excel Table 'tblIntake'</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Bluestone Memorial Hospital: the 4 West bed board (36 beds, 12/31/2025) and the ED intake log (Dec 25–31, 2025), plus 12 monthly census CSV files covering all 18 inpatient units in the health system in 2025 (6,570 rows).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Bluestone Memorial Hospital: the 4 West bed board (36 beds, 12/31/2025) and the ED intake log (Dec 25–31, 2025), plus 12 monthly census CSV files covering all 18 inpatient units in the health system in 2025 (6,570 rows).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -1149,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="96" customHeight="1">
+    <row r="6" ht="111" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2</t>
@@ -1177,7 +1201,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>EnableEvents belongs to the whole Excel application, not to one workbook or sheet. It stays False after the macro stops, for every open workbook, until something sets it back. That's why every handler that turns it off needs an error handler that always turns it back on. The EventsOn macro in modLog does the same job from Alt + F8 (Mac: Developer → Macros).</t>
+          <t>EnableEvents belongs to the whole Excel application, not to one workbook or sheet. It stays False after the macro stops, for every open workbook, until something sets it back. That's why every handler that turns it off needs an error handler that always turns it back on. The EventsOn macro in modLog does the same job from Alt + F8 (Mac: Option + F8, or Developer → Macros).</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1483,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>The table started with 69 arrivals, and three valid saves make 72. If you see 73, the 6-digit MRN got through, so check your Like "########" test (# matches exactly one digit). An extra, half-empty row instead means a run-time error stopped AddIntakeRow after ListRows.Add: delete that row (right-click → Delete → Table Rows) and fix the error. ListRows.Add grows the Table itself, so formats, formulas and anything that refers to tblIntake pick up the new row automatically. The full form code is in solutions/frmIntake.vba.</t>
+          <t>The table started with 69 arrivals, and three valid saves make 72. If you see 73, the 6-digit MRN got through, so check your Like "########" test (# matches exactly one digit). An extra, half-empty row instead means a run-time error stopped AddIntakeRow after ListRows.Add: delete that row (right-click → Delete → Table Rows) and fix the error. ListRows.Add grows the Table itself, so formats, formulas, and anything that refers to tblIntake pick up the new row automatically. The full form code is in solutions/frmIntake.vba.</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1554,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Option buttons don't share a single value, so SelectedESI asks optESI1 to optESI5 in turn and returns the number of the one that's selected (0 if none, which validation rejects). Writing that Long keeps ESILevel numeric, so COUNTIFS, AVERAGE and PivotTables all work. 17 of the original 69 arrivals were ESI 1–2, and Jennifer Rice (ESI 2) brings the total to 18.</t>
+          <t>Option buttons don't share a single value, so SelectedESI asks optESI1 to optESI5 in turn and returns the number of the one that's selected (0 if none, which validation rejects). Writing that Long keeps ESILevel numeric, so COUNTIFS, AVERAGE, and PivotTables all work. 17 of the original 69 arrivals were ESI 1–2, and Jennifer Rice (ESI 2) brings the total to 18.</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1875,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>The macro reads Combined into an array once, then loops in memory. That's far faster than reading cells one by one. A Collection maps each DeptID to its position in the parallel arrays (UnitIndex returns 0 for a new unit), which works on Windows and Mac. Scripting.Dictionary (Lesson 5.4) would also work, but it's Windows-only. DateSerial(y, m + 1, 0) returns the last day of the month, so the same code handles 28-, 30- and 31-day months.</t>
+          <t>The macro reads Combined into an array once, then loops in memory. That's far faster than reading cells one by one. A Collection maps each DeptID to its position in the parallel arrays (UnitIndex returns 0 for a new unit), which works on Windows and Mac. Scripting.Dictionary (Lesson 5.4) would also work, but it's Windows-only. DateSerial(y, m + 1, 0) returns the last day of the month, so the same code handles 28-, 30-, and 31-day months.</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2172,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Compare Save, SaveAs and SaveCopyAs in Guide §9</t>
+          <t>Compare Save, SaveAs, and SaveCopyAs in Guide §9</t>
         </is>
       </c>
       <c r="D9" s="23" t="n"/>
@@ -3099,7 +3123,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Bed status" error="Choose Occupied, Clean, Dirty or Blocked." type="list">
+    <dataValidation sqref="C2:C37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Bed status" error="Choose Occupied, Clean, Dirty, or Blocked." type="list">
       <formula1>"Occupied,Clean,Dirty,Blocked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/05-automation-vba/05-events-userforms-automation/5.5-events-userforms-automation.xlsx
+++ b/05-automation-vba/05-events-userforms-automation/5.5-events-userforms-automation.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="B2:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -739,7 +739,6 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -761,7 +760,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -818,7 +816,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -839,7 +836,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -847,7 +844,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type answers in the yellow cells. The gray cells fill in by themselves once your macros have run.</t>
+          <t>Go to the 'Practice' sheet. Type your answers for tasks 1–5 and 12 in the yellow cells. For tasks 6–11, finish and run your macros, and the gray cells fill in by themselves.</t>
         </is>
       </c>
     </row>
@@ -895,7 +892,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Save this file as an Excel Macro-Enabled Workbook (.xlsm) before you write any code: File → Save As → Excel Macro-Enabled Workbook.</t>
+          <t>Macros can't be saved in an .xlsx file. Before you write any code, choose File → Save As and pick 'Excel Macro-Enabled Workbook (*.xlsm)'.</t>
         </is>
       </c>
     </row>
@@ -911,7 +908,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
+    <row r="20" ht="63" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -919,11 +916,11 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Starter code: the lesson's starter folder. Import the .bas files with File → Import File… in the VBE. Paste the .cls and .vba files into the module named at the top of each file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+          <t>Starter code is in the lesson's starter/ folder. Open the Visual Basic Editor with Alt + F11 (Mac: Option + F11, or Developer → Visual Basic), then choose File → Import File… for modLog.bas and modReports.bas. Don't import the .cls and .vba files: paste each one into the module named at the top of the file (ThisWorkbook, the BedBoard sheet, or the frmIntake form you build in Guide §7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -931,11 +928,10 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Other sheets: Log (WriteLog appends a row here), Combined (CombineCensusFiles fills it from the CSV files), Settings (cells the report macros read and write), Lists (drop-down lists for the intake form).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t>The bonus macro creates Report_yyyy-mm sheets. The gray cells on the Bonus sheet read them, so they stay blank until the macro has run.</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
@@ -992,7 +988,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -1040,34 +1035,82 @@
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Log</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Timestamp, Event, Detail, User. WriteLog adds a row here each time your code calls it (tasks 6–7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Headers only. CombineCensusFiles fills it with the rows of the 12 monthly census CSV files (tasks 11–12 and the bonus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>ReportMonth, CsvFolder, ReportFolder, and LastExport: the cells your report macros read and write (task 11 and the bonus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Arrival modes and chief complaints for the intake form's drop-down lists (tasks 8–10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>The bonus challenge (5 parts).</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
+    <row r="38" ht="48" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>About the data</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Bluestone Memorial Hospital: the 4 West bed board (36 beds, 12/31/2025) and the ED intake log (Dec 25–31, 2025), plus 12 monthly census CSV files covering all 18 inpatient units in the health system in 2025 (6,570 rows).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -1329,7 +1372,7 @@
     WriteLog "Open", "Opened by " &amp; Application.UserName
     Me.Worksheets("BedBoard").Activate
 End Sub
-' Runs just before every save (Ctrl+S, File &gt; Save, Save As).
+' Runs just before every save (Ctrl + S, File &gt; Save, Save As).
 ' Setting Cancel = True stops the save.
 Private Sub Workbook_BeforeSave(ByVal SaveAsUI As Boolean, Cancel As Boolean)
     Dim lo As ListObject
@@ -1370,7 +1413,7 @@
         <is>
           <t>Paste starter/BedBoard.cls into the BedBoard sheet's module and finish its Worksheet_Change handler. For each changed Status cell it should stamp StatusTime with Now and call WriteLog "Bed status", … once. Delete any "Bed status" rows that your testing left on the Log sheet, then make exactly these edits:
 • Change 4W-405B's Status to Dirty.
-• Select the Status cells of 4W-410A, 4W-410B and 4W-411A, type Clean, and press Ctrl + Enter (Mac: ⌘ + Return) to fill all three at once.
+• Select the Status cells of 4W-410A, 4W-410B, and 4W-411A, type Clean, and press Ctrl + Enter (Mac: ⌘ + Return) to fill all three at once.
 • In 4W-415A's Notes cell, type Bed alarm on.
 The gray cell counts the Log's "Bed status" rows.</t>
         </is>
@@ -2053,7 +2096,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
+          <t>Type your answers for tasks 1–5 and 12 in the yellow cells. The gray cells for tasks 6–11 fill in once your macros have run. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2284,7 @@
         <is>
           <t>Paste starter/BedBoard.cls into the BedBoard sheet's module and finish its Worksheet_Change handler. For each changed Status cell it should stamp StatusTime with Now and call WriteLog "Bed status", … once. Delete any "Bed status" rows that your testing left on the Log sheet, then make exactly these edits:
 • Change 4W-405B's Status to Dirty.
-• Select the Status cells of 4W-410A, 4W-410B and 4W-411A, type Clean, and press Ctrl + Enter (Mac: ⌘ + Return) to fill all three at once.
+• Select the Status cells of 4W-410A, 4W-410B, and 4W-411A, type Clean, and press Ctrl + Enter (Mac: ⌘ + Return) to fill all three at once.
 • In 4W-415A's Notes cell, type Bed alarm on.
 The gray cell counts the Log's "Bed status" rows.</t>
         </is>
@@ -6803,7 +6846,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>There's nothing to type on this sheet. The gray cells fill in once BuildCensusReport has run for December and January, and the Check column turns green when they match. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
